--- a/FedMilLiPstCT.xlsx
+++ b/FedMilLiPstCT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\FedGMil\csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C1795FC-570E-4E53-9B3C-05EEF4059706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975DD5E3-3252-4FDD-9584-DF82185B120A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36C93FBD-4E81-441C-9FA0-C13D74F35AC9}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>COMMAND_TIER</t>
   </si>
   <si>
-    <t>FEDERAL_AGENCY_BRANCH</t>
-  </si>
-  <si>
     <t>REQUIRED_REPLENISHMENT_UNITS</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>US Army</t>
+  </si>
+  <si>
+    <t>Agency</t>
   </si>
 </sst>
 </file>
@@ -731,18 +731,6 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -839,6 +827,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -846,18 +843,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -874,14 +874,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB49A27E-9CCB-42C4-B45D-CEBAD8E0C060}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB49A27E-9CCB-42C4-B45D-CEBAD8E0C060}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E11" xr:uid="{AB49A27E-9CCB-42C4-B45D-CEBAD8E0C060}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{86B04A82-E0EE-48B9-8497-3CCB49FC301B}" name="COMMAND_TIER" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{7621439E-0F6D-4371-9A2E-0269E711302D}" name="FEDERAL_AGENCY_BRANCH" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{227C6CB3-19F8-4CEC-9DD9-D4DBA2987D3D}" name="REQUIRED_REPLENISHMENT_UNITS" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{683981BC-195B-4FCB-9A44-78A39E7C1883}" name=" AVERAGE_UNIT_COST_MSRP " dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{11D3DFB8-10A2-4E14-AFE4-F21C9123E858}" name=" ESTIMATED_REMEDIATION_BUDGET " dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{86B04A82-E0EE-48B9-8497-3CCB49FC301B}" name="COMMAND_TIER" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{7621439E-0F6D-4371-9A2E-0269E711302D}" name="Agency" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{227C6CB3-19F8-4CEC-9DD9-D4DBA2987D3D}" name="REQUIRED_REPLENISHMENT_UNITS" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{683981BC-195B-4FCB-9A44-78A39E7C1883}" name=" AVERAGE_UNIT_COST_MSRP " dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{11D3DFB8-10A2-4E14-AFE4-F21C9123E858}" name=" ESTIMATED_REMEDIATION_BUDGET " dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1219,24 +1219,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>10547</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
         <v>9863</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>9179</v>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <v>8495</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>7811</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="1">
         <v>7120</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1">
         <v>6241</v>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>5899</v>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>5215</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="9">
         <v>2489</v>
